--- a/documentation/MLOps_UseCase_API_Design.xlsx
+++ b/documentation/MLOps_UseCase_API_Design.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Lumiere\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Lumiere\Back_Lumiere\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98675CFB-2053-4C6A-A180-077C40B807F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3057B2B7-09D7-4926-BF94-43EB9D825EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="719" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="admin-delete" sheetId="16" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="138">
   <si>
     <t>DELETE</t>
   </si>
@@ -140,13 +140,7 @@
     <t>GET</t>
   </si>
   <si>
-    <t>get the current config of [DEV_ID] from DB</t>
-  </si>
-  <si>
     <t>need details from Patrick</t>
-  </si>
-  <si>
-    <t>get details of all assets from DB</t>
   </si>
   <si>
     <t>[{
@@ -171,9 +165,6 @@
 },… ]</t>
   </si>
   <si>
-    <t>get details of all assets in [GROUP_ID] from DB</t>
-  </si>
-  <si>
     <t>GROUP_ID</t>
   </si>
   <si>
@@ -270,35 +261,7 @@
     <t>POST</t>
   </si>
   <si>
-    <t>create/update config for [DEV_ID] to DB</t>
-  </si>
-  <si>
     <t>create/update asset for [ASSET_ID] to DB</t>
-  </si>
-  <si>
-    <t>return latest location of passed tag</t>
-  </si>
-  <si>
-    <t>[{_x000D_
-  "x": number,_x000D_
-  "y": number,_x000D_
-  "z": 3,_x000D_
-  "id": "string",_x000D_
-  "name": "string",_x000D_
-  "type": "string",_x000D_
-  "timestamp": "string"_x000D_
-}, …]</t>
-  </si>
-  <si>
-    <t>[{_x000D_
-  "x": 1,_x000D_
-  "y": 2,_x000D_
-  "z": 3,_x000D_
-  "id": "9037",_x000D_
-  "name": "F2",_x000D_
-  "type": "AGV",_x000D_
-  "timestamp": "2019-01-09T18:55:17+00:00"_x000D_
-}, …]</t>
   </si>
   <si>
     <t>return an array of latest locations of all tags, for passed group</t>
@@ -747,6 +710,106 @@
   }
 }</t>
     <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Retrieve a saved skin analysis result and its metadata from the database by its unique identifier.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>analyze_id</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  "id": "ana_xxxxxxxx (string)",
+  "created_at": "ISO8601 timestamp",
+  "tom_geral_fitzpatrick": 3,
+  "tom_geral_hex": "#RRGGBB",
+  "fitzpatrick_source": "claude",
+  "subtom_predominante": "frio",
+  "regioes": {},
+  "comparacao_tons": {},
+  "imperfeicoes": [],
+  "recommendations": [],
+  "skin_tone": {}
+}</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Not Found: Analysis result not found for the given ID.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Internal Server Error: Internal error while fetching the analysis from database.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Service health check and live monitoring of API status and Core Database connectivity.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  "status": "ok",
+  "service": "skin-analyzer",
+  "db": "ok"
+}</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Returns "db": "unreachable" if the database connection fails.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monitor the execution source of the skin analyzer pipeline to detect model degradation (e.g., high ratio of 'claude' fallback over local 'bisenet').</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Metrics successfully calculated and retrieved.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  "timestamp": "ISO8601 timestamp",
+  "bisenet_success_rate": 0.95,
+  "claude_fallback_count": 5,
+  "status": "NORMAL"
+}</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Internal Server Error: Failed to generate monitoring statistics.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Create a new user account and profile in the system database, including required application-specific fields and initial user metadata.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  "username": "string (required, unique)",
+  "email": "string (required, valid email address)",
+  "password": "string (required, hashed on backend)",
+  "profile": {
+    "first_name": "string",
+    "last_name": "string",
+    "age": "integer",
+    "skin_type_self_assessed": "string (e.g., oily, dry, combination)"
+  }
+}</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Created: Account created successfully and stored in the database.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bad Request: Username or email already exists, or missing required fields.</t>
+  </si>
+  <si>
+    <t>Unprocessable Entity: Invalid data format (e.g., poorly formatted email).</t>
+  </si>
+  <si>
+    <t>Internal Server Error: Internal database error during user creation.</t>
   </si>
 </sst>
 </file>
@@ -1156,7 +1219,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1193,22 +1256,31 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1228,6 +1300,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1237,6 +1311,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1246,10 +1338,12 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1268,19 +1362,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1288,84 +1376,71 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1690,7 +1765,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="34"/>
+      <c r="A1" s="41"/>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1703,63 +1778,63 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="34"/>
-      <c r="B2" s="41" t="s">
+      <c r="A2" s="41"/>
+      <c r="B2" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="52"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="34"/>
+      <c r="A3" s="41"/>
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="25"/>
+      <c r="C3" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="54"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="34"/>
+      <c r="A4" s="41"/>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="37"/>
+      <c r="D4" s="44"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="34"/>
-      <c r="B5" s="41" t="s">
+      <c r="A5" s="41"/>
+      <c r="B5" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="42"/>
-      <c r="D5" s="43"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="52"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="34"/>
+      <c r="A6" s="41"/>
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="25"/>
+      <c r="C6" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="54"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="34"/>
+      <c r="A7" s="41"/>
       <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="37"/>
+      <c r="D7" s="44"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="34"/>
+      <c r="A8" s="41"/>
       <c r="B8" s="2"/>
       <c r="C8" s="3" t="s">
         <v>11</v>
@@ -1769,25 +1844,25 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="34"/>
+      <c r="A9" s="41"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="27"/>
+      <c r="D9" s="56"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="34"/>
+      <c r="A10" s="41"/>
       <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="37"/>
+      <c r="D10" s="44"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="35"/>
+      <c r="A11" s="42"/>
       <c r="B11" s="5" t="s">
         <v>0</v>
       </c>
@@ -1800,63 +1875,63 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="35"/>
-      <c r="B12" s="38" t="s">
+      <c r="A12" s="42"/>
+      <c r="B12" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="39"/>
-      <c r="D12" s="40"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="47"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="35"/>
+      <c r="A13" s="42"/>
       <c r="B13" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="31"/>
+      <c r="C13" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="49"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="35"/>
+      <c r="A14" s="42"/>
       <c r="B14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="33"/>
+      <c r="D14" s="40"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="35"/>
-      <c r="B15" s="38" t="s">
+      <c r="A15" s="42"/>
+      <c r="B15" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="40"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="47"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="35"/>
+      <c r="A16" s="42"/>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="31"/>
+      <c r="C16" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="49"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="35"/>
+      <c r="A17" s="42"/>
       <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="33"/>
+      <c r="D17" s="40"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="35"/>
+      <c r="A18" s="42"/>
       <c r="B18" s="6"/>
       <c r="C18" s="5" t="s">
         <v>11</v>
@@ -1866,25 +1941,27 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="35"/>
+      <c r="A19" s="42"/>
       <c r="B19" s="6"/>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="29"/>
+      <c r="D19" s="58"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="35"/>
+      <c r="A20" s="42"/>
       <c r="B20" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="33"/>
+      <c r="D20" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="A1:A10"/>
     <mergeCell ref="A11:A20"/>
@@ -1901,8 +1978,6 @@
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1911,85 +1986,85 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="64.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="55.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="82.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="34"/>
+      <c r="A1" s="80">
+        <v>3</v>
+      </c>
       <c r="B1" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C1" s="2" t="str">
-        <f>API!$A$1 &amp; "/devices/config/[DEV_ID]"&amp; API!$A$2</f>
-        <v>http://localhost:8001/devices/config/[DEV_ID]</v>
+        <f>API!$A$1 &amp; "/api/analyze/{analyze_id}"&amp; API!$A$2</f>
+        <v>http://localhost:8001/api/analyze/{analyze_id}</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>20</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="34"/>
-      <c r="B2" s="41" t="s">
+      <c r="A2" s="81"/>
+      <c r="B2" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="52"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="34"/>
+      <c r="A3" s="81"/>
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="25"/>
+      <c r="C3" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="54"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="34"/>
+      <c r="A4" s="81"/>
       <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="37"/>
+        <v>121</v>
+      </c>
+      <c r="C4" s="43"/>
+      <c r="D4" s="44"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="34"/>
-      <c r="B5" s="41" t="s">
+      <c r="A5" s="81"/>
+      <c r="B5" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="42"/>
-      <c r="D5" s="43"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="52"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="34"/>
+      <c r="A6" s="81"/>
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="25"/>
+      <c r="C6" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="54"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="34"/>
-      <c r="B7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="36" t="s">
+      <c r="A7" s="81"/>
+      <c r="B7" s="2">
+        <v>200</v>
+      </c>
+      <c r="C7" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="37"/>
+      <c r="D7" s="44"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="34"/>
+      <c r="A8" s="81"/>
       <c r="B8" s="2"/>
       <c r="C8" s="3" t="s">
         <v>11</v>
@@ -1998,670 +2073,682 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="34"/>
+    <row r="9" spans="1:4" ht="204.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="81"/>
       <c r="B9" s="2"/>
       <c r="C9" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="81"/>
+      <c r="B10" s="2">
+        <v>400</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="44"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="85"/>
+      <c r="B11" s="2">
+        <v>500</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="D11" s="44"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="103">
+        <v>4</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="6" t="str">
+        <f>API!$A$1 &amp; "/"&amp; API!$A$2</f>
+        <v>http://localhost:8001/</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="104"/>
+      <c r="B13" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="46"/>
+      <c r="D13" s="47"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="104"/>
+      <c r="B14" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="49"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="104"/>
+      <c r="B15" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="46"/>
+      <c r="D15" s="47"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="104"/>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="49"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="104"/>
+      <c r="B17" s="6">
+        <v>200</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="40"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="104"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="104"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D19" s="7"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="105"/>
+      <c r="B20" s="6">
+        <v>400</v>
+      </c>
+      <c r="C20" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="D20" s="40"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="74"/>
+      <c r="B21" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="9" t="str">
+        <f>API!$A$1 &amp; "/"&amp; API!$A$2</f>
+        <v>http://localhost:8001/</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="74"/>
+      <c r="B22" s="63" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="64"/>
+      <c r="D22" s="65"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="74"/>
+      <c r="B23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="44"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="74"/>
+      <c r="B24" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="61" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="62"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="74"/>
+      <c r="B25" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="64"/>
+      <c r="D25" s="65"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="74"/>
+      <c r="B26" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="61" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" s="62"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="74"/>
+      <c r="B27" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="59" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="60"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="74"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="74"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="34"/>
-      <c r="B10" s="2" t="s">
+      <c r="D29" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="74"/>
+      <c r="B30" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C30" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="37"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="35"/>
-      <c r="B11" s="5" t="s">
+      <c r="D30" s="60"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="75"/>
+      <c r="B31" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="6" t="str">
-        <f>API!$A$1 &amp; "/assets"&amp; API!$A$2</f>
-        <v>http://localhost:8001/assets</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="35"/>
-      <c r="B12" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="39"/>
-      <c r="D12" s="40"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="35"/>
-      <c r="B13" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="31"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="35"/>
-      <c r="B14" s="38" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="39"/>
-      <c r="D14" s="40"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="35"/>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="31"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="35"/>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="33"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="35"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="35"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="35"/>
-      <c r="B19" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="33"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="34"/>
-      <c r="B20" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="9" t="str">
-        <f>API!$A$1 &amp; "/assets/[GROUP_ID]"&amp; API!$A$2</f>
-        <v>http://localhost:8001/assets/[GROUP_ID]</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="34"/>
-      <c r="B21" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="45"/>
-      <c r="D21" s="46"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="34"/>
-      <c r="B22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="37"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="34"/>
-      <c r="B23" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C23" s="47" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="48"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="34"/>
-      <c r="B24" s="44" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="45"/>
-      <c r="D24" s="46"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="34"/>
-      <c r="B25" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="47" t="s">
-        <v>4</v>
-      </c>
-      <c r="D25" s="48"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="34"/>
-      <c r="B26" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" s="49" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="50"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="34"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="34"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="34"/>
-      <c r="B29" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="50"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="35"/>
-      <c r="B30" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C30" s="6" t="str">
+      <c r="C31" s="6" t="str">
         <f>API!$A$1 &amp; "/assets/anchors/[GROUP_ID]"&amp; API!$A$2</f>
         <v>http://localhost:8001/assets/anchors/[GROUP_ID]</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="35"/>
-      <c r="B31" s="38" t="s">
+      <c r="D31" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="75"/>
+      <c r="B32" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="39"/>
-      <c r="D31" s="40"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="35"/>
-      <c r="B32" s="5" t="s">
+      <c r="C32" s="46"/>
+      <c r="D32" s="47"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="75"/>
+      <c r="B33" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C32" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D32" s="31"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="35"/>
-      <c r="B33" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C33" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="D33" s="33"/>
+      <c r="C33" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="49"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="35"/>
-      <c r="B34" s="38" t="s">
+      <c r="A34" s="75"/>
+      <c r="B34" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" s="40"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="75"/>
+      <c r="B35" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="39"/>
-      <c r="D34" s="40"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="35"/>
-      <c r="B35" s="5" t="s">
+      <c r="C35" s="46"/>
+      <c r="D35" s="47"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="75"/>
+      <c r="B36" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C35" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D35" s="31"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="35"/>
-      <c r="B36" s="6" t="s">
+      <c r="C36" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" s="49"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="75"/>
+      <c r="B37" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="32" t="s">
+      <c r="C37" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="D36" s="33"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="35"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="5" t="s">
+      <c r="D37" s="40"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="75"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D38" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="35"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="35"/>
-      <c r="B39" s="6" t="s">
+    <row r="39" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="75"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="75"/>
+      <c r="B40" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="32" t="s">
+      <c r="C40" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="33"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="34"/>
-      <c r="B40" s="3" t="s">
+      <c r="D40" s="40"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="41"/>
+      <c r="B41" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="2" t="str">
+      <c r="C41" s="2" t="str">
         <f>API!$A$1 &amp; "/assets/tags/[GROUP_ID]"&amp; API!$A$2</f>
         <v>http://localhost:8001/assets/tags/[GROUP_ID]</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="34"/>
-      <c r="B41" s="41" t="s">
+      <c r="D41" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="41"/>
+      <c r="B42" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="42"/>
-      <c r="D41" s="43"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="34"/>
-      <c r="B42" s="3" t="s">
+      <c r="C42" s="51"/>
+      <c r="D42" s="52"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="41"/>
+      <c r="B43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D42" s="25"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="34"/>
-      <c r="B43" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C43" s="36" t="s">
+      <c r="C43" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" s="54"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="41"/>
+      <c r="B44" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C44" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44" s="44"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="41"/>
+      <c r="B45" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="51"/>
+      <c r="D45" s="52"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="41"/>
+      <c r="B46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" s="54"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="41"/>
+      <c r="B47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="44"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="41"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="41"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D43" s="37"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="34"/>
-      <c r="B44" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="42"/>
-      <c r="D44" s="43"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="34"/>
-      <c r="B45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D45" s="25"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="34"/>
-      <c r="B46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" s="37"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="34"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="34"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="34"/>
-      <c r="B49" s="2" t="s">
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="41"/>
+      <c r="B50" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C49" s="36" t="s">
+      <c r="C50" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="D49" s="37"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="35"/>
-      <c r="B50" s="5" t="s">
+      <c r="D50" s="44"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="42"/>
+      <c r="B51" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C50" s="6" t="str">
+      <c r="C51" s="6" t="str">
         <f>API!$A$1 &amp; "/asset/asset/[ASSET_ID]"&amp; API!$A$2</f>
         <v>http://localhost:8001/asset/asset/[ASSET_ID]</v>
       </c>
-      <c r="D50" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="35"/>
-      <c r="B51" s="38" t="s">
+      <c r="D51" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="42"/>
+      <c r="B52" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C51" s="39"/>
-      <c r="D51" s="40"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="35"/>
-      <c r="B52" s="5" t="s">
+      <c r="C52" s="46"/>
+      <c r="D52" s="47"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="42"/>
+      <c r="B53" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C52" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D52" s="31"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="35"/>
-      <c r="B53" s="6" t="s">
+      <c r="C53" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53" s="49"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="42"/>
+      <c r="B54" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="32" t="s">
+      <c r="C54" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="D53" s="33"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="35"/>
-      <c r="B54" s="38" t="s">
+      <c r="D54" s="40"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="42"/>
+      <c r="B55" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C54" s="39"/>
-      <c r="D54" s="40"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="35"/>
-      <c r="B55" s="5" t="s">
+      <c r="C55" s="46"/>
+      <c r="D55" s="47"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="42"/>
+      <c r="B56" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C55" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D55" s="31"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="35"/>
-      <c r="B56" s="6" t="s">
+      <c r="C56" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56" s="49"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="42"/>
+      <c r="B57" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C56" s="32" t="s">
+      <c r="C57" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="D56" s="33"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="35"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="5" t="s">
+      <c r="D57" s="40"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="42"/>
+      <c r="B58" s="6"/>
+      <c r="C58" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="D58" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="35"/>
-      <c r="B58" s="6"/>
-      <c r="C58" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="35"/>
-      <c r="B59" s="6" t="s">
+    <row r="59" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="42"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="42"/>
+      <c r="B60" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C59" s="32" t="s">
+      <c r="C60" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="D59" s="33"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="34"/>
-      <c r="B60" s="3" t="s">
+      <c r="D60" s="40"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="41"/>
+      <c r="B61" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C60" s="2" t="str">
+      <c r="C61" s="2" t="str">
         <f>API!$A$1 &amp; "/asset/device/[DEV_ID]"&amp; API!$A$2</f>
         <v>http://localhost:8001/asset/device/[DEV_ID]</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="34"/>
-      <c r="B61" s="41" t="s">
+      <c r="D61" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="41"/>
+      <c r="B62" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C61" s="42"/>
-      <c r="D61" s="43"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="34"/>
-      <c r="B62" s="3" t="s">
+      <c r="C62" s="51"/>
+      <c r="D62" s="52"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="41"/>
+      <c r="B63" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C62" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D62" s="25"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="34"/>
-      <c r="B63" s="2" t="s">
+      <c r="C63" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D63" s="54"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="41"/>
+      <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C63" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="D63" s="37"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="34"/>
-      <c r="B64" s="41" t="s">
+      <c r="C64" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="D64" s="44"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="41"/>
+      <c r="B65" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="42"/>
-      <c r="D64" s="43"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="34"/>
-      <c r="B65" s="3" t="s">
+      <c r="C65" s="51"/>
+      <c r="D65" s="52"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="41"/>
+      <c r="B66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D65" s="25"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="34"/>
-      <c r="B66" s="2" t="s">
+      <c r="C66" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D66" s="54"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="41"/>
+      <c r="B67" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C66" s="36" t="s">
+      <c r="C67" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="D66" s="37"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="34"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="3" t="s">
+      <c r="D67" s="44"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="41"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D68" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="34"/>
-      <c r="B68" s="2"/>
-      <c r="C68" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="34"/>
-      <c r="B69" s="2" t="s">
+    <row r="69" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A69" s="41"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="41"/>
+      <c r="B70" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C69" s="36" t="s">
+      <c r="C70" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="D69" s="37"/>
+      <c r="D70" s="44"/>
     </row>
   </sheetData>
-  <mergeCells count="55">
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="A1:A10"/>
-    <mergeCell ref="A11:A19"/>
-    <mergeCell ref="A20:A29"/>
-    <mergeCell ref="A30:A39"/>
-    <mergeCell ref="A40:A49"/>
-    <mergeCell ref="A50:A59"/>
-    <mergeCell ref="A60:A69"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="B24:D24"/>
+  <mergeCells count="56">
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="C15:D15"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="B5:D5"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="A1:A11"/>
+    <mergeCell ref="A12:A20"/>
+    <mergeCell ref="A21:A30"/>
+    <mergeCell ref="A31:A40"/>
+    <mergeCell ref="A41:A50"/>
+    <mergeCell ref="A51:A60"/>
+    <mergeCell ref="A61:A70"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="B55:D55"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2676,84 +2763,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="34"/>
+      <c r="A1" s="41"/>
       <c r="B1" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C1" s="2" t="str">
         <f>API!$A$1 &amp; "/devices/config/[DEV_ID]"&amp; API!$A$2</f>
         <v>http://localhost:8001/devices/config/[DEV_ID]</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="34"/>
-      <c r="B2" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="53"/>
+      <c r="A2" s="41"/>
+      <c r="B2" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="69"/>
+      <c r="D2" s="70"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="34"/>
-      <c r="B3" s="41" t="s">
+      <c r="A3" s="41"/>
+      <c r="B3" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="43"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="52"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="34"/>
+      <c r="A4" s="41"/>
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="25"/>
+      <c r="C4" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="54"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="34"/>
+      <c r="A5" s="41"/>
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="37"/>
+      <c r="D5" s="44"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="34"/>
-      <c r="B6" s="41" t="s">
+      <c r="A6" s="41"/>
+      <c r="B6" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="43"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="52"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="34"/>
+      <c r="A7" s="41"/>
       <c r="B7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="25"/>
+      <c r="C7" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="54"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="34"/>
+      <c r="A8" s="41"/>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="37"/>
+      <c r="D8" s="44"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="34"/>
+      <c r="A9" s="41"/>
       <c r="B9" s="2"/>
       <c r="C9" s="3" t="s">
         <v>11</v>
@@ -2763,104 +2850,104 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="34"/>
+      <c r="A10" s="41"/>
       <c r="B10" s="2"/>
       <c r="C10" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="34"/>
+      <c r="A11" s="41"/>
       <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="37"/>
+      <c r="D11" s="44"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="35"/>
+      <c r="A12" s="42"/>
       <c r="B12" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C12" s="6" t="str">
         <f>API!$A$1 &amp; "/devices/status/[DEV_ID]"&amp; API!$A$2</f>
         <v>http://localhost:8001/devices/status/[DEV_ID]</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="35"/>
-      <c r="B13" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="55"/>
-      <c r="D13" s="56"/>
+      <c r="A13" s="42"/>
+      <c r="B13" s="71" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="72"/>
+      <c r="D13" s="73"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="35"/>
-      <c r="B14" s="38" t="s">
+      <c r="A14" s="42"/>
+      <c r="B14" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="39"/>
-      <c r="D14" s="40"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="47"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="35"/>
+      <c r="A15" s="42"/>
       <c r="B15" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="31"/>
+      <c r="C15" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="49"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="35"/>
+      <c r="A16" s="42"/>
       <c r="B16" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="33"/>
+      <c r="D16" s="40"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="35"/>
-      <c r="B17" s="38" t="s">
+      <c r="A17" s="42"/>
+      <c r="B17" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="39"/>
-      <c r="D17" s="40"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="47"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="35"/>
+      <c r="A18" s="42"/>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="31"/>
+      <c r="C18" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="49"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="35"/>
+      <c r="A19" s="42"/>
       <c r="B19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="32" t="s">
+      <c r="C19" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="33"/>
+      <c r="D19" s="40"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="35"/>
+      <c r="A20" s="42"/>
       <c r="B20" s="6"/>
       <c r="C20" s="5" t="s">
         <v>11</v>
@@ -2870,104 +2957,104 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="35"/>
+      <c r="A21" s="42"/>
       <c r="B21" s="6"/>
       <c r="C21" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="35"/>
+      <c r="A22" s="42"/>
       <c r="B22" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="32" t="s">
+      <c r="C22" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="33"/>
+      <c r="D22" s="40"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="34"/>
+      <c r="A23" s="41"/>
       <c r="B23" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C23" s="2" t="str">
         <f>API!$A$1 &amp; "/devices/restart/[DEV_ID]"&amp; API!$A$2</f>
         <v>http://localhost:8001/devices/restart/[DEV_ID]</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="34"/>
-      <c r="B24" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="52"/>
-      <c r="D24" s="53"/>
+      <c r="A24" s="41"/>
+      <c r="B24" s="68" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="69"/>
+      <c r="D24" s="70"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="34"/>
-      <c r="B25" s="41" t="s">
+      <c r="A25" s="41"/>
+      <c r="B25" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="42"/>
-      <c r="D25" s="43"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="52"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="34"/>
+      <c r="A26" s="41"/>
       <c r="B26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C26" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D26" s="25"/>
+      <c r="C26" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" s="54"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="34"/>
+      <c r="A27" s="41"/>
       <c r="B27" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="36" t="s">
+      <c r="C27" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="D27" s="37"/>
+      <c r="D27" s="44"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="34"/>
-      <c r="B28" s="41" t="s">
+      <c r="A28" s="41"/>
+      <c r="B28" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="42"/>
-      <c r="D28" s="43"/>
+      <c r="C28" s="51"/>
+      <c r="D28" s="52"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="34"/>
+      <c r="A29" s="41"/>
       <c r="B29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29" s="25"/>
+      <c r="C29" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" s="54"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="34"/>
+      <c r="A30" s="41"/>
       <c r="B30" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="36" t="s">
+      <c r="C30" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="37"/>
+      <c r="D30" s="44"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="34"/>
+      <c r="A31" s="41"/>
       <c r="B31" s="2"/>
       <c r="C31" s="3" t="s">
         <v>11</v>
@@ -2977,114 +3064,114 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="34"/>
+      <c r="A32" s="41"/>
       <c r="B32" s="2"/>
       <c r="C32" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="34"/>
+      <c r="A33" s="41"/>
       <c r="B33" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="36" t="s">
+      <c r="C33" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="37"/>
+      <c r="D33" s="44"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="35"/>
+      <c r="A34" s="42"/>
       <c r="B34" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C34" s="6" t="str">
         <f>API!$A$1 &amp; "/devices/gpio/[DEV_ID]/[MASK]"&amp; API!$A$2</f>
         <v>http://localhost:8001/devices/gpio/[DEV_ID]/[MASK]</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="35"/>
-      <c r="B35" s="54" t="s">
-        <v>44</v>
-      </c>
-      <c r="C35" s="55"/>
-      <c r="D35" s="56"/>
+      <c r="A35" s="42"/>
+      <c r="B35" s="71" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" s="72"/>
+      <c r="D35" s="73"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="35"/>
-      <c r="B36" s="38" t="s">
+      <c r="A36" s="42"/>
+      <c r="B36" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="39"/>
-      <c r="D36" s="40"/>
+      <c r="C36" s="46"/>
+      <c r="D36" s="47"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="35"/>
+      <c r="A37" s="42"/>
       <c r="B37" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C37" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D37" s="31"/>
+      <c r="C37" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" s="49"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="35"/>
+      <c r="A38" s="42"/>
       <c r="B38" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C38" s="32" t="s">
+      <c r="C38" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="D38" s="33"/>
+      <c r="D38" s="40"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="35"/>
+      <c r="A39" s="42"/>
       <c r="B39" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C39" s="57" t="s">
-        <v>46</v>
-      </c>
-      <c r="D39" s="58"/>
+        <v>42</v>
+      </c>
+      <c r="C39" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="D39" s="67"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="35"/>
-      <c r="B40" s="38" t="s">
+      <c r="A40" s="42"/>
+      <c r="B40" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C40" s="39"/>
-      <c r="D40" s="40"/>
+      <c r="C40" s="46"/>
+      <c r="D40" s="47"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="35"/>
+      <c r="A41" s="42"/>
       <c r="B41" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C41" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D41" s="31"/>
+      <c r="C41" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" s="49"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="35"/>
+      <c r="A42" s="42"/>
       <c r="B42" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="32" t="s">
+      <c r="C42" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="D42" s="33"/>
+      <c r="D42" s="40"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="35"/>
+      <c r="A43" s="42"/>
       <c r="B43" s="6"/>
       <c r="C43" s="5" t="s">
         <v>11</v>
@@ -3094,104 +3181,104 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="35"/>
+      <c r="A44" s="42"/>
       <c r="B44" s="6"/>
       <c r="C44" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="35"/>
+      <c r="A45" s="42"/>
       <c r="B45" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C45" s="32" t="s">
+      <c r="C45" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="D45" s="33"/>
+      <c r="D45" s="40"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="34"/>
+      <c r="A46" s="41"/>
       <c r="B46" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C46" s="2" t="str">
         <f>API!$A$1 &amp; "/devices/rt/[DEV_ID]"&amp; API!$A$2</f>
         <v>http://localhost:8001/devices/rt/[DEV_ID]</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="34"/>
-      <c r="B47" s="51" t="s">
-        <v>48</v>
-      </c>
-      <c r="C47" s="52"/>
-      <c r="D47" s="53"/>
+      <c r="A47" s="41"/>
+      <c r="B47" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="C47" s="69"/>
+      <c r="D47" s="70"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="34"/>
-      <c r="B48" s="41" t="s">
+      <c r="A48" s="41"/>
+      <c r="B48" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C48" s="42"/>
-      <c r="D48" s="43"/>
+      <c r="C48" s="51"/>
+      <c r="D48" s="52"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="34"/>
+      <c r="A49" s="41"/>
       <c r="B49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C49" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D49" s="25"/>
+      <c r="C49" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D49" s="54"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="34"/>
+      <c r="A50" s="41"/>
       <c r="B50" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="36" t="s">
+      <c r="C50" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="D50" s="37"/>
+      <c r="D50" s="44"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="34"/>
-      <c r="B51" s="41" t="s">
+      <c r="A51" s="41"/>
+      <c r="B51" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="C51" s="42"/>
-      <c r="D51" s="43"/>
+      <c r="C51" s="51"/>
+      <c r="D51" s="52"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="34"/>
+      <c r="A52" s="41"/>
       <c r="B52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C52" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D52" s="25"/>
+      <c r="C52" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" s="54"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="34"/>
+      <c r="A53" s="41"/>
       <c r="B53" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C53" s="36" t="s">
+      <c r="C53" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="D53" s="37"/>
+      <c r="D53" s="44"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="34"/>
+      <c r="A54" s="41"/>
       <c r="B54" s="2"/>
       <c r="C54" s="3" t="s">
         <v>11</v>
@@ -3201,27 +3288,57 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="34"/>
+      <c r="A55" s="41"/>
       <c r="B55" s="2"/>
       <c r="C55" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="34"/>
+      <c r="A56" s="41"/>
       <c r="B56" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C56" s="36" t="s">
+      <c r="C56" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="D56" s="37"/>
+      <c r="D56" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="A1:A11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
     <mergeCell ref="A12:A22"/>
     <mergeCell ref="A23:A33"/>
     <mergeCell ref="A34:A45"/>
@@ -3238,36 +3355,6 @@
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="B48:D48"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="A1:A11"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="C18:D18"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3277,85 +3364,83 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="53.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="108" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="34"/>
+      <c r="A1" s="74">
+        <v>6</v>
+      </c>
       <c r="B1" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C1" s="2" t="str">
-        <f>API!$A$1 &amp; "/devices/config/[DEV_ID]"&amp; API!$A$2</f>
-        <v>http://localhost:8001/devices/config/[DEV_ID]</v>
+        <f>API!$A$1 &amp; "/api/users/register"&amp; API!$A$2</f>
+        <v>http://localhost:8001/api/users/register</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="34"/>
-      <c r="B2" s="41" t="s">
+      <c r="A2" s="74"/>
+      <c r="B2" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="52"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="34"/>
+      <c r="A3" s="74"/>
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="25"/>
+      <c r="C3" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="54"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="34"/>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="37"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="44"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="34"/>
-      <c r="B5" s="41" t="s">
+      <c r="A5" s="74"/>
+      <c r="B5" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="42"/>
-      <c r="D5" s="43"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="52"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="34"/>
+      <c r="A6" s="74"/>
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="25"/>
+      <c r="C6" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="54"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="34"/>
-      <c r="B7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="37"/>
+      <c r="A7" s="74"/>
+      <c r="B7" s="2">
+        <v>201</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" s="44"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="34"/>
+      <c r="A8" s="74"/>
       <c r="B8" s="2"/>
       <c r="C8" s="3" t="s">
         <v>11</v>
@@ -3364,138 +3449,157 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="34"/>
+    <row r="9" spans="1:4" ht="189" x14ac:dyDescent="0.25">
+      <c r="A9" s="74"/>
       <c r="B9" s="2"/>
       <c r="C9" s="4" t="s">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="34"/>
-      <c r="B10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="37"/>
+      <c r="A10" s="74"/>
+      <c r="B10" s="2">
+        <v>400</v>
+      </c>
+      <c r="C10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D10" s="106"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="35"/>
-      <c r="B11" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="6" t="str">
+      <c r="A11" s="74"/>
+      <c r="B11" s="2">
+        <v>422</v>
+      </c>
+      <c r="C11" t="s">
+        <v>136</v>
+      </c>
+      <c r="D11" s="106"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="74"/>
+      <c r="B12" s="2">
+        <v>500</v>
+      </c>
+      <c r="C12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" s="106"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="42"/>
+      <c r="B13" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="6" t="str">
         <f>API!$A$1 &amp; "/asset/[ASSET_ID]"&amp; API!$A$2</f>
         <v>http://localhost:8001/asset/[ASSET_ID]</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="35"/>
-      <c r="B12" s="38" t="s">
+      <c r="D13" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="42"/>
+      <c r="B14" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="39"/>
-      <c r="D12" s="40"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="35"/>
-      <c r="B13" s="5" t="s">
+      <c r="C14" s="46"/>
+      <c r="D14" s="47"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="42"/>
+      <c r="B15" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="31"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="35"/>
-      <c r="B14" s="6" t="s">
+      <c r="C15" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="49"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="42"/>
+      <c r="B16" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C16" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="33"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="35"/>
-      <c r="B15" s="38" t="s">
+      <c r="D16" s="40"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="42"/>
+      <c r="B17" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="40"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="35"/>
-      <c r="B16" s="5" t="s">
+      <c r="C17" s="46"/>
+      <c r="D17" s="47"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="42"/>
+      <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="31"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="35"/>
-      <c r="B17" s="6" t="s">
+      <c r="C18" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="49"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="42"/>
+      <c r="B19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C19" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="33"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="35"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="5" t="s">
+      <c r="D19" s="40"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="42"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="35"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="35"/>
-      <c r="B20" s="6" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="42"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="42"/>
+      <c r="B22" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C22" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="33"/>
+      <c r="D22" s="40"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="15">
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A1:A12"/>
+    <mergeCell ref="A13:A22"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A1:A10"/>
-    <mergeCell ref="A11:A20"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B17:D17"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="C4:D4"/>
@@ -3509,7 +3613,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D99"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
@@ -3518,1081 +3622,1066 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="59"/>
+      <c r="A1" s="74">
+        <v>5</v>
+      </c>
       <c r="B1" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C1" s="2" t="str">
-        <f>API!$A$1 &amp; "/tracking/point/[GROUP_ID]/[DEV_ID]"&amp; API!$A$2</f>
-        <v>http://localhost:8001/tracking/point/[GROUP_ID]/[DEV_ID]</v>
+        <f>API!$A$1 &amp; "/api/monitor/fallback-metrics"&amp; API!$A$2</f>
+        <v>http://localhost:8001/api/monitor/fallback-metrics</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="59"/>
-      <c r="B2" s="41" t="s">
+      <c r="A2" s="74"/>
+      <c r="B2" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="52"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="59"/>
+      <c r="A3" s="74"/>
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="25"/>
+      <c r="C3" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="54"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="59"/>
-      <c r="B4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="37"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="44"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="59"/>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="37"/>
+      <c r="A5" s="74"/>
+      <c r="B5" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="51"/>
+      <c r="D5" s="52"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="59"/>
-      <c r="B6" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="43"/>
+      <c r="A6" s="74"/>
+      <c r="B6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="54"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="59"/>
-      <c r="B7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="25"/>
+      <c r="A7" s="74"/>
+      <c r="B7" s="2">
+        <v>200</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="44"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="59"/>
-      <c r="B8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="37"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="59"/>
+      <c r="A8" s="74"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="123.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="74"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="123.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="59"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>54</v>
-      </c>
+      <c r="C9" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="74"/>
+      <c r="B10" s="2">
+        <v>500</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="D10" s="44"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="59"/>
-      <c r="B11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="37"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="61"/>
-      <c r="B12" s="5" t="s">
+      <c r="A11" s="75"/>
+      <c r="B11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="6" t="str">
+      <c r="C11" s="6" t="str">
         <f>API!$A$1 &amp; "/tracking/points/[GROUP_ID]/"&amp; API!$A$2</f>
         <v>http://localhost:8001/tracking/points/[GROUP_ID]/</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>55</v>
-      </c>
+      <c r="D11" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="75"/>
+      <c r="B12" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="76"/>
+      <c r="D12" s="49"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="61"/>
-      <c r="B13" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" s="60"/>
-      <c r="D13" s="31"/>
+      <c r="A13" s="75"/>
+      <c r="B13" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="49"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="61"/>
-      <c r="B14" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="31"/>
+      <c r="A14" s="75"/>
+      <c r="B14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="40"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="61"/>
-      <c r="B15" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="33"/>
+      <c r="A15" s="75"/>
+      <c r="B15" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="76"/>
+      <c r="D15" s="49"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="61"/>
-      <c r="B16" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="60"/>
-      <c r="D16" s="31"/>
+      <c r="A16" s="75"/>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="49"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="61"/>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="31"/>
+      <c r="A17" s="75"/>
+      <c r="B17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="40"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="61"/>
-      <c r="B18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="33"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="61"/>
+      <c r="A18" s="75"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="75"/>
       <c r="B19" s="6"/>
-      <c r="C19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="61"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>57</v>
-      </c>
+      <c r="C19" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="75"/>
+      <c r="B20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="40"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="61"/>
-      <c r="B21" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="33"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="59"/>
-      <c r="B22" s="3" t="s">
+      <c r="A21" s="74"/>
+      <c r="B21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="2" t="str">
+      <c r="C21" s="2" t="str">
         <f>API!$A$1 &amp; "/historic/point/[GROUP_ID]/[DEV_ID]/[START_DATETIME]/[END_DATETIME]"&amp; API!$A$2</f>
         <v>http://localhost:8001/historic/point/[GROUP_ID]/[DEV_ID]/[START_DATETIME]/[END_DATETIME]</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="74"/>
+      <c r="B22" s="53" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="77"/>
+      <c r="D22" s="54"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="74"/>
+      <c r="B23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="54"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="74"/>
+      <c r="B24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="44"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="74"/>
+      <c r="B25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="44"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="74"/>
+      <c r="B26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="74"/>
+      <c r="B27" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="74"/>
+      <c r="B28" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="77"/>
+      <c r="D28" s="54"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="74"/>
+      <c r="B29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" s="54"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="74"/>
+      <c r="B30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="44"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="74"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="74"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="59"/>
-      <c r="B23" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="62"/>
-      <c r="D23" s="25"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="59"/>
-      <c r="B24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" s="25"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="59"/>
-      <c r="B25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="37"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="59"/>
-      <c r="B26" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="37"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="59"/>
-      <c r="B27" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="59"/>
-      <c r="B28" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="59"/>
-      <c r="B29" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="62"/>
-      <c r="D29" s="25"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="59"/>
-      <c r="B30" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D30" s="25"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="59"/>
-      <c r="B31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="37"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="59"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="59"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>65</v>
-      </c>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="74"/>
+      <c r="B33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="44"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="59"/>
-      <c r="B34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="37"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="61"/>
-      <c r="B35" s="5" t="s">
+      <c r="A34" s="75"/>
+      <c r="B34" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C35" s="6" t="str">
+      <c r="C34" s="6" t="str">
         <f>API!$A$1 &amp; "/historic/points/[GROUP_ID]/[START_DATETIME]/[END_DATETIME]"&amp; API!$A$2</f>
         <v>http://localhost:8001/historic/points/[GROUP_ID]/[START_DATETIME]/[END_DATETIME]</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>66</v>
-      </c>
+      <c r="D34" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="75"/>
+      <c r="B35" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="76"/>
+      <c r="D35" s="49"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="61"/>
-      <c r="B36" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="60"/>
-      <c r="D36" s="31"/>
+      <c r="A36" s="75"/>
+      <c r="B36" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" s="49"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="61"/>
-      <c r="B37" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C37" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D37" s="31"/>
+      <c r="A37" s="75"/>
+      <c r="B37" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" s="40"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="61"/>
+      <c r="A38" s="75"/>
       <c r="B38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C38" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="D38" s="33"/>
+        <v>52</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="61"/>
+      <c r="A39" s="75"/>
       <c r="B39" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C39" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="75"/>
+      <c r="B40" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="76"/>
+      <c r="D40" s="49"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="75"/>
+      <c r="B41" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" s="49"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="75"/>
+      <c r="B42" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="40"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="75"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="75"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="61"/>
-      <c r="B40" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="61"/>
-      <c r="B41" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="60"/>
-      <c r="D41" s="31"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="61"/>
-      <c r="B42" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D42" s="31"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="61"/>
-      <c r="B43" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C43" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="33"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="61"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="61"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="D44" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="75"/>
+      <c r="B45" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" s="40"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="61"/>
-      <c r="B46" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C46" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="D46" s="33"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="59"/>
-      <c r="B47" s="3" t="s">
+      <c r="A46" s="74"/>
+      <c r="B46" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C47" s="2" t="str">
+      <c r="C46" s="2" t="str">
         <f>API!$A$1 &amp; "/assets/anchors/[GROUP_ID]"&amp; API!$A$2</f>
         <v>http://localhost:8001/assets/anchors/[GROUP_ID]</v>
       </c>
-      <c r="D47" s="2" t="s">
-        <v>68</v>
-      </c>
+      <c r="D46" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="74"/>
+      <c r="B47" s="53" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="77"/>
+      <c r="D47" s="54"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="59"/>
-      <c r="B48" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="62"/>
-      <c r="D48" s="25"/>
+      <c r="A48" s="74"/>
+      <c r="B48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C48" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D48" s="54"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="59"/>
-      <c r="B49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C49" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D49" s="25"/>
+      <c r="A49" s="74"/>
+      <c r="B49" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C49" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" s="44"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="59"/>
+      <c r="A50" s="74"/>
       <c r="B50" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C50" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="D50" s="37"/>
+        <v>5</v>
+      </c>
+      <c r="C50" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" s="44"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="59"/>
+      <c r="A51" s="74"/>
       <c r="B51" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C51" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="D51" s="37"/>
+        <v>52</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="59"/>
+      <c r="A52" s="74"/>
       <c r="B52" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="59"/>
-      <c r="B53" s="2" t="s">
+      <c r="A53" s="74"/>
+      <c r="B53" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="77"/>
+      <c r="D53" s="54"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="74"/>
+      <c r="B54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D54" s="54"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="74"/>
+      <c r="B55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="44"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="74"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A57" s="74"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="D57" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="59"/>
-      <c r="B54" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="62"/>
-      <c r="D54" s="25"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="59"/>
-      <c r="B55" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C55" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D55" s="25"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="59"/>
-      <c r="B56" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C56" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="D56" s="37"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="59"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A58" s="59"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>70</v>
-      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="74"/>
+      <c r="B58" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" s="44"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="59"/>
-      <c r="B59" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C59" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="D59" s="37"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="61"/>
-      <c r="B60" s="5" t="s">
+      <c r="A59" s="75"/>
+      <c r="B59" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C60" s="6" t="str">
+      <c r="C59" s="6" t="str">
         <f>API!$A$1 &amp; "/groups"&amp; API!$A$2</f>
         <v>http://localhost:8001/groups</v>
       </c>
-      <c r="D60" s="6" t="s">
-        <v>71</v>
-      </c>
+      <c r="D59" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="75"/>
+      <c r="B60" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="76"/>
+      <c r="D60" s="49"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="61"/>
-      <c r="B61" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="60"/>
-      <c r="D61" s="31"/>
+      <c r="A61" s="75"/>
+      <c r="B61" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C61" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D61" s="49"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="61"/>
-      <c r="B62" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C62" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D62" s="31"/>
+      <c r="A62" s="75"/>
+      <c r="B62" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="76"/>
+      <c r="D62" s="49"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="61"/>
-      <c r="B63" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="60"/>
-      <c r="D63" s="31"/>
+      <c r="A63" s="75"/>
+      <c r="B63" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D63" s="49"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="61"/>
-      <c r="B64" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C64" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D64" s="31"/>
+      <c r="A64" s="75"/>
+      <c r="B64" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C64" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" s="40"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="61"/>
-      <c r="B65" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C65" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="D65" s="33"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="61"/>
+      <c r="A65" s="75"/>
+      <c r="B65" s="6"/>
+      <c r="C65" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="75"/>
       <c r="B66" s="6"/>
-      <c r="C66" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="61"/>
-      <c r="B67" s="6"/>
-      <c r="C67" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>73</v>
-      </c>
+      <c r="C66" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="75"/>
+      <c r="B67" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C67" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" s="40"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="61"/>
-      <c r="B68" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C68" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="D68" s="33"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="59"/>
-      <c r="B69" s="3" t="s">
+      <c r="A68" s="74"/>
+      <c r="B68" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C69" s="2" t="str">
+      <c r="C68" s="2" t="str">
         <f>API!$A$1 &amp; "/groups/[APP_ID]"&amp; API!$A$2</f>
         <v>http://localhost:8001/groups/[APP_ID]</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>74</v>
-      </c>
+      <c r="D68" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="74"/>
+      <c r="B69" s="53" t="s">
+        <v>2</v>
+      </c>
+      <c r="C69" s="77"/>
+      <c r="D69" s="54"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="59"/>
-      <c r="B70" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="C70" s="62"/>
-      <c r="D70" s="25"/>
+      <c r="A70" s="74"/>
+      <c r="B70" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C70" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D70" s="54"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="59"/>
-      <c r="B71" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C71" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D71" s="25"/>
+      <c r="A71" s="74"/>
+      <c r="B71" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C71" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="59"/>
-      <c r="B72" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C72" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>77</v>
-      </c>
+      <c r="A72" s="74"/>
+      <c r="B72" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="77"/>
+      <c r="D72" s="54"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="59"/>
-      <c r="B73" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C73" s="62"/>
-      <c r="D73" s="25"/>
+      <c r="A73" s="74"/>
+      <c r="B73" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D73" s="54"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="59"/>
-      <c r="B74" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C74" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D74" s="25"/>
+      <c r="A74" s="74"/>
+      <c r="B74" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C74" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D74" s="44"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="59"/>
-      <c r="B75" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C75" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="D75" s="37"/>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="59"/>
+      <c r="A75" s="74"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A76" s="74"/>
       <c r="B76" s="2"/>
-      <c r="C76" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A77" s="59"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>73</v>
-      </c>
+      <c r="C76" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="74"/>
+      <c r="B77" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C77" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" s="44"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="59"/>
-      <c r="B78" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C78" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="D78" s="37"/>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="61"/>
-      <c r="B79" s="5" t="s">
+      <c r="A78" s="75"/>
+      <c r="B78" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C79" s="6" t="str">
+      <c r="C78" s="6" t="str">
         <f>API!$A$1 &amp; "/config/[APP_ID]"&amp; API!$A$2</f>
         <v>http://localhost:8001/config/[APP_ID]</v>
       </c>
-      <c r="D79" s="6" t="s">
-        <v>78</v>
-      </c>
+      <c r="D78" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="75"/>
+      <c r="B79" s="13"/>
+      <c r="C79" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D79" s="14"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="61"/>
-      <c r="B80" s="13"/>
-      <c r="C80" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D80" s="14"/>
+      <c r="A80" s="75"/>
+      <c r="B80" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="C80" s="76"/>
+      <c r="D80" s="49"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="61"/>
-      <c r="B81" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="C81" s="60"/>
-      <c r="D81" s="31"/>
+      <c r="A81" s="75"/>
+      <c r="B81" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C81" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D81" s="49"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="61"/>
-      <c r="B82" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C82" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D82" s="31"/>
+      <c r="A82" s="75"/>
+      <c r="B82" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C82" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="61"/>
-      <c r="B83" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C83" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>77</v>
-      </c>
+      <c r="A83" s="75"/>
+      <c r="B83" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="76"/>
+      <c r="D83" s="49"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="61"/>
-      <c r="B84" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C84" s="60"/>
-      <c r="D84" s="31"/>
+      <c r="A84" s="75"/>
+      <c r="B84" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C84" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D84" s="49"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="61"/>
-      <c r="B85" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C85" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D85" s="31"/>
+      <c r="A85" s="75"/>
+      <c r="B85" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C85" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="D85" s="40"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="61"/>
-      <c r="B86" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C86" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="D86" s="33"/>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="61"/>
+      <c r="A86" s="75"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="252" x14ac:dyDescent="0.25">
+      <c r="A87" s="75"/>
       <c r="B87" s="6"/>
-      <c r="C87" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" ht="252" x14ac:dyDescent="0.25">
-      <c r="A88" s="61"/>
-      <c r="B88" s="6"/>
-      <c r="C88" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>81</v>
-      </c>
+      <c r="C87" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="75"/>
+      <c r="B88" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C88" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88" s="40"/>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="61"/>
-      <c r="B89" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C89" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="D89" s="33"/>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="59"/>
-      <c r="B90" s="3" t="s">
+      <c r="A89" s="74"/>
+      <c r="B89" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C90" s="2" t="str">
+      <c r="C89" s="2" t="str">
         <f>API!$A$1 &amp; "/config/group/[GROUP_ID]"&amp; API!$A$2</f>
         <v>http://localhost:8001/config/group/[GROUP_ID]</v>
       </c>
-      <c r="D90" s="2" t="s">
-        <v>82</v>
-      </c>
+      <c r="D89" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="74"/>
+      <c r="B90" s="15"/>
+      <c r="C90" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D90" s="16"/>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="59"/>
-      <c r="B91" s="15"/>
-      <c r="C91" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D91" s="16"/>
+      <c r="A91" s="74"/>
+      <c r="B91" s="53" t="s">
+        <v>2</v>
+      </c>
+      <c r="C91" s="77"/>
+      <c r="D91" s="54"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="59"/>
-      <c r="B92" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="C92" s="62"/>
-      <c r="D92" s="25"/>
+      <c r="A92" s="74"/>
+      <c r="B92" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C92" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D92" s="54"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="59"/>
-      <c r="B93" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C93" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D93" s="25"/>
+      <c r="A93" s="74"/>
+      <c r="B93" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C93" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D93" s="2"/>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="59"/>
-      <c r="B94" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C94" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="D94" s="2"/>
+      <c r="A94" s="74"/>
+      <c r="B94" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="77"/>
+      <c r="D94" s="54"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="59"/>
-      <c r="B95" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C95" s="62"/>
-      <c r="D95" s="25"/>
+      <c r="A95" s="74"/>
+      <c r="B95" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C95" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D95" s="54"/>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="59"/>
-      <c r="B96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C96" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D96" s="25"/>
+      <c r="A96" s="74"/>
+      <c r="B96" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D96" s="44"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="59"/>
-      <c r="B97" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C97" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="D97" s="37"/>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="59"/>
+      <c r="A97" s="74"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A98" s="74"/>
       <c r="B98" s="2"/>
-      <c r="C98" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="59"/>
-      <c r="B99" s="2"/>
-      <c r="C99" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="59"/>
-      <c r="B100" s="2" t="s">
+      <c r="C98" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="74"/>
+      <c r="B99" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C100" s="36" t="s">
+      <c r="C99" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="D100" s="37"/>
+      <c r="D99" s="44"/>
     </row>
   </sheetData>
-  <mergeCells count="71">
-    <mergeCell ref="A1:A11"/>
-    <mergeCell ref="A12:A21"/>
-    <mergeCell ref="A22:A34"/>
-    <mergeCell ref="A35:A46"/>
-    <mergeCell ref="A47:A59"/>
+  <mergeCells count="70">
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="A89:A99"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="A78:A88"/>
+    <mergeCell ref="B91:D91"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="A68:A77"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="A59:A67"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B15:D15"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="A60:A68"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="A69:A78"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="A90:A100"/>
-    <mergeCell ref="B81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="A79:A89"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="A1:A10"/>
+    <mergeCell ref="A11:A20"/>
+    <mergeCell ref="A21:A33"/>
+    <mergeCell ref="A34:A45"/>
+    <mergeCell ref="A46:A58"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4611,7 +4700,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="59">
+      <c r="A1" s="74">
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -4622,65 +4711,65 @@
         <v>http://localhost:8001/</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="1" customFormat="1" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="59"/>
-      <c r="B2" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="C2" s="63"/>
-      <c r="D2" s="64"/>
+      <c r="A2" s="74"/>
+      <c r="B2" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="79"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="59"/>
-      <c r="B3" s="41" t="s">
+      <c r="A3" s="74"/>
+      <c r="B3" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="43"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="52"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="59"/>
+      <c r="A4" s="74"/>
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="25"/>
+      <c r="C4" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="54"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="59"/>
-      <c r="B5" s="41" t="s">
+      <c r="A5" s="74"/>
+      <c r="B5" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="42"/>
-      <c r="D5" s="43"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="52"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="59"/>
+      <c r="A6" s="74"/>
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="25"/>
+      <c r="C6" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="54"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="59"/>
+      <c r="A7" s="74"/>
       <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="37"/>
+      <c r="D7" s="44"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="59"/>
+      <c r="A8" s="74"/>
       <c r="B8" s="2"/>
       <c r="C8" s="3" t="s">
         <v>11</v>
@@ -4690,24 +4779,24 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="59"/>
+      <c r="A9" s="74"/>
       <c r="B9" s="2"/>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="59"/>
+      <c r="A10" s="74"/>
       <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="37"/>
+      <c r="D10" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4737,423 +4826,425 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="71">
+      <c r="A1" s="89">
         <v>2</v>
       </c>
-      <c r="B1" s="72" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="73" t="str">
+      <c r="B1" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="26" t="str">
         <f>API!$A$1 &amp; "/api/analyze"&amp; API!$A$2</f>
         <v>http://localhost:8001/api/analyze</v>
       </c>
-      <c r="D1" s="74" t="s">
-        <v>104</v>
+      <c r="D1" s="27" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="75"/>
-      <c r="B2" s="41" t="s">
+      <c r="A2" s="90"/>
+      <c r="B2" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="76"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="95"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="75"/>
+      <c r="A3" s="90"/>
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="77"/>
+      <c r="C3" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="96"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="75"/>
+      <c r="A4" s="90"/>
       <c r="B4" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D4" s="78"/>
+        <v>98</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="86"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="75"/>
-      <c r="B5" s="41" t="s">
+      <c r="A5" s="90"/>
+      <c r="B5" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="42"/>
-      <c r="D5" s="76"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="95"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="75"/>
+      <c r="A6" s="90"/>
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="77"/>
+      <c r="C6" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="96"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="75"/>
-      <c r="B7" s="67">
+      <c r="A7" s="90"/>
+      <c r="B7" s="80">
         <v>200</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="78"/>
+      <c r="D7" s="86"/>
     </row>
     <row r="8" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="75"/>
-      <c r="B8" s="68"/>
+      <c r="A8" s="90"/>
+      <c r="B8" s="81"/>
       <c r="C8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="79" t="s">
+      <c r="D8" s="28" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="75"/>
-      <c r="B9" s="69"/>
-      <c r="C9" s="66" t="s">
-        <v>125</v>
-      </c>
-      <c r="D9" s="80" t="s">
-        <v>126</v>
+      <c r="A9" s="90"/>
+      <c r="B9" s="85"/>
+      <c r="C9" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="75"/>
-      <c r="B10" s="67">
+      <c r="A10" s="90"/>
+      <c r="B10" s="80">
         <v>400</v>
       </c>
-      <c r="C10" s="70" t="s">
-        <v>113</v>
-      </c>
-      <c r="D10" s="81"/>
+      <c r="C10" s="83" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" s="84"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="75"/>
-      <c r="B11" s="68"/>
+      <c r="A11" s="90"/>
+      <c r="B11" s="81"/>
       <c r="C11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="79" t="s">
+      <c r="D11" s="28" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="75"/>
-      <c r="B12" s="69"/>
-      <c r="C12" s="66" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" s="80" t="s">
+      <c r="A12" s="90"/>
+      <c r="B12" s="85"/>
+      <c r="C12" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="90"/>
+      <c r="B13" s="80">
+        <v>413</v>
+      </c>
+      <c r="C13" s="83" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="75"/>
-      <c r="B13" s="67">
-        <v>413</v>
-      </c>
-      <c r="C13" s="70" t="s">
-        <v>114</v>
-      </c>
-      <c r="D13" s="81"/>
+      <c r="D13" s="84"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="75"/>
-      <c r="B14" s="68"/>
+      <c r="A14" s="90"/>
+      <c r="B14" s="81"/>
       <c r="C14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="79" t="s">
+      <c r="D14" s="28" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="75"/>
-      <c r="B15" s="69"/>
-      <c r="C15" s="66" t="s">
-        <v>112</v>
-      </c>
-      <c r="D15" s="80" t="s">
-        <v>115</v>
+      <c r="A15" s="90"/>
+      <c r="B15" s="85"/>
+      <c r="C15" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="75"/>
-      <c r="B16" s="67">
+      <c r="A16" s="90"/>
+      <c r="B16" s="80">
         <v>422</v>
       </c>
-      <c r="C16" s="70" t="s">
-        <v>116</v>
-      </c>
-      <c r="D16" s="81"/>
+      <c r="C16" s="83" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="84"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="75"/>
-      <c r="B17" s="68"/>
+      <c r="A17" s="90"/>
+      <c r="B17" s="81"/>
       <c r="C17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="79" t="s">
+      <c r="D17" s="28" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="75"/>
-      <c r="B18" s="69"/>
-      <c r="C18" s="66" t="s">
-        <v>112</v>
-      </c>
-      <c r="D18" s="80" t="s">
-        <v>117</v>
+      <c r="A18" s="90"/>
+      <c r="B18" s="85"/>
+      <c r="C18" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" s="29" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="75"/>
-      <c r="B19" s="67">
+      <c r="A19" s="90"/>
+      <c r="B19" s="80">
         <v>500</v>
       </c>
-      <c r="C19" s="70" t="s">
-        <v>118</v>
-      </c>
-      <c r="D19" s="81"/>
+      <c r="C19" s="83" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="84"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="75"/>
-      <c r="B20" s="68"/>
+      <c r="A20" s="90"/>
+      <c r="B20" s="81"/>
       <c r="C20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="79" t="s">
+      <c r="D20" s="28" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="82"/>
-      <c r="B21" s="83"/>
-      <c r="C21" s="84" t="s">
+      <c r="A21" s="91"/>
+      <c r="B21" s="82"/>
+      <c r="C21" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="D21" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="D21" s="85" t="s">
-        <v>119</v>
-      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="86"/>
-      <c r="B22" s="87" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" s="88" t="str">
+      <c r="A22" s="92"/>
+      <c r="B22" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="33" t="str">
         <f>API!$A$1 &amp; "/devices/status/[DEV_ID]"&amp; API!$A$2</f>
         <v>http://localhost:8001/devices/status/[DEV_ID]</v>
       </c>
-      <c r="D22" s="89" t="s">
-        <v>120</v>
+      <c r="D22" s="34" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="90"/>
-      <c r="B23" s="38" t="s">
+      <c r="A23" s="93"/>
+      <c r="B23" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="39"/>
-      <c r="D23" s="91"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="97"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="90"/>
+      <c r="A24" s="93"/>
       <c r="B24" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" s="92"/>
+      <c r="C24" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="98"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="90"/>
+      <c r="A25" s="93"/>
       <c r="B25" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C25" s="32" t="s">
-        <v>122</v>
-      </c>
-      <c r="D25" s="93"/>
+        <v>114</v>
+      </c>
+      <c r="C25" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" s="99"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="90"/>
-      <c r="B26" s="38" t="s">
+      <c r="A26" s="93"/>
+      <c r="B26" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="39"/>
-      <c r="D26" s="91"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="97"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="90"/>
+      <c r="A27" s="93"/>
       <c r="B27" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D27" s="92"/>
+      <c r="C27" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" s="98"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="90"/>
+      <c r="A28" s="93"/>
       <c r="B28" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="32" t="s">
+      <c r="C28" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="93"/>
+      <c r="D28" s="99"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="90"/>
+      <c r="A29" s="93"/>
       <c r="B29" s="6"/>
       <c r="C29" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="94" t="s">
+      <c r="D29" s="35" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="90"/>
+      <c r="A30" s="93"/>
       <c r="B30" s="6"/>
       <c r="C30" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="D30" s="80" t="s">
-        <v>123</v>
+        <v>116</v>
+      </c>
+      <c r="D30" s="29" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="95"/>
-      <c r="B31" s="96" t="s">
+      <c r="A31" s="94"/>
+      <c r="B31" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="C31" s="97" t="s">
-        <v>124</v>
-      </c>
-      <c r="D31" s="98"/>
+      <c r="C31" s="100" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" s="101"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="71"/>
-      <c r="B32" s="72" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" s="73" t="str">
+      <c r="A32" s="89"/>
+      <c r="B32" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="26" t="str">
         <f>API!$A$1 &amp; "/devices/rt/[DEV_ID]"&amp; API!$A$2</f>
         <v>http://localhost:8001/devices/rt/[DEV_ID]</v>
       </c>
-      <c r="D32" s="74" t="s">
-        <v>87</v>
+      <c r="D32" s="27" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="75"/>
-      <c r="B33" s="41" t="s">
+      <c r="A33" s="90"/>
+      <c r="B33" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C33" s="42"/>
-      <c r="D33" s="76"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="95"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="75"/>
+      <c r="A34" s="90"/>
       <c r="B34" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C34" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D34" s="77"/>
+      <c r="C34" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" s="96"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="75"/>
+      <c r="A35" s="90"/>
       <c r="B35" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="36" t="s">
+      <c r="C35" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="D35" s="78"/>
+      <c r="D35" s="86"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="75"/>
-      <c r="B36" s="41" t="s">
+      <c r="A36" s="90"/>
+      <c r="B36" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="42"/>
-      <c r="D36" s="76"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="95"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="75"/>
+      <c r="A37" s="90"/>
       <c r="B37" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D37" s="77"/>
+      <c r="C37" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" s="96"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="75"/>
+      <c r="A38" s="90"/>
       <c r="B38" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="36" t="s">
+      <c r="C38" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="D38" s="78"/>
+      <c r="D38" s="86"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="75"/>
+      <c r="A39" s="90"/>
       <c r="B39" s="2"/>
       <c r="C39" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D39" s="79" t="s">
+      <c r="D39" s="28" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="75"/>
+      <c r="A40" s="90"/>
       <c r="B40" s="2"/>
       <c r="C40" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D40" s="99" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="D40" s="37" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="82"/>
-      <c r="B41" s="100" t="s">
+      <c r="A41" s="91"/>
+      <c r="B41" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="C41" s="101" t="s">
+      <c r="C41" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="D41" s="102"/>
+      <c r="D41" s="88"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="B7:B9"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="C41:D41"/>
     <mergeCell ref="A1:A21"/>
@@ -5170,15 +5261,13 @@
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="C24:D24"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="C16:D16"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5197,24 +5286,24 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C1" s="18"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -5257,15 +5346,15 @@
       </c>
       <c r="B7" t="str">
         <f>IFERROR(VLOOKUP($A7,'listener-get'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A7,'listener-post'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A7,'andon-get'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A7,'admin-delete'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A7,'admin-get'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A7,'admin-put'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A7,'admin-post'!$A:$D,2,FALSE),"")))))))</f>
-        <v/>
+        <v>GET</v>
       </c>
       <c r="C7" t="str">
         <f>IFERROR(VLOOKUP($A7,'listener-get'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A7,'listener-post'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A7,'andon-get'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A7,'admin-delete'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A7,'admin-get'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A7,'admin-put'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A7,'admin-post'!$A:$D,3,FALSE),"")))))))</f>
-        <v/>
+        <v>http://localhost:8001/api/analyze/{analyze_id}</v>
       </c>
       <c r="D7" s="19" t="str">
         <f>IF(IFERROR(MATCH(A7,'listener-get'!$A:$A,0),"")&lt;&gt;"","listener-get",IF(IFERROR(MATCH(A7,'listener-post'!$A:$A,0),"")&lt;&gt;"","listener-post",IF(IFERROR(MATCH(A7,'andon-get'!$A:$A,0),"")&lt;&gt;"","andon-get",IF(IFERROR(MATCH(A7,'admin-post'!$A:$A,0),"")&lt;&gt;"","admin-post",IF(IFERROR(MATCH(A7,'admin-put'!$A:$A,0),"")&lt;&gt;"","admin-put",IF(IFERROR(MATCH(A7,'admin-get'!$A:$A,0),"")&lt;&gt;"","admin-get",IF(IFERROR(MATCH(A7,'admin-delete'!$A:$A,0),"")&lt;&gt;"","admin-delete","")))))))</f>
-        <v/>
+        <v>admin-get</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -5274,15 +5363,15 @@
       </c>
       <c r="B8" t="str">
         <f>IFERROR(VLOOKUP($A8,'listener-get'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A8,'listener-post'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A8,'andon-get'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A8,'admin-delete'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A8,'admin-get'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A8,'admin-put'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A8,'admin-post'!$A:$D,2,FALSE),"")))))))</f>
-        <v/>
+        <v>GET</v>
       </c>
       <c r="C8" t="str">
         <f>IFERROR(VLOOKUP($A8,'listener-get'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A8,'listener-post'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A8,'andon-get'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A8,'admin-delete'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A8,'admin-get'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A8,'admin-put'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A8,'admin-post'!$A:$D,3,FALSE),"")))))))</f>
-        <v/>
+        <v>http://localhost:8001/</v>
       </c>
       <c r="D8" s="19" t="str">
         <f>IF(IFERROR(MATCH(A8,'listener-get'!$A:$A,0),"")&lt;&gt;"","listener-get",IF(IFERROR(MATCH(A8,'listener-post'!$A:$A,0),"")&lt;&gt;"","listener-post",IF(IFERROR(MATCH(A8,'andon-get'!$A:$A,0),"")&lt;&gt;"","andon-get",IF(IFERROR(MATCH(A8,'admin-post'!$A:$A,0),"")&lt;&gt;"","admin-post",IF(IFERROR(MATCH(A8,'admin-put'!$A:$A,0),"")&lt;&gt;"","admin-put",IF(IFERROR(MATCH(A8,'admin-get'!$A:$A,0),"")&lt;&gt;"","admin-get",IF(IFERROR(MATCH(A8,'admin-delete'!$A:$A,0),"")&lt;&gt;"","admin-delete","")))))))</f>
-        <v/>
+        <v>admin-get</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -5291,15 +5380,15 @@
       </c>
       <c r="B9" t="str">
         <f>IFERROR(VLOOKUP($A9,'listener-get'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A9,'listener-post'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A9,'andon-get'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A9,'admin-delete'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A9,'admin-get'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A9,'admin-put'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A9,'admin-post'!$A:$D,2,FALSE),"")))))))</f>
-        <v/>
+        <v>GET</v>
       </c>
       <c r="C9" t="str">
         <f>IFERROR(VLOOKUP($A9,'listener-get'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A9,'listener-post'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A9,'andon-get'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A9,'admin-delete'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A9,'admin-get'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A9,'admin-put'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A9,'admin-post'!$A:$D,3,FALSE),"")))))))</f>
-        <v/>
+        <v>http://localhost:8001/api/monitor/fallback-metrics</v>
       </c>
       <c r="D9" s="19" t="str">
         <f>IF(IFERROR(MATCH(A9,'listener-get'!$A:$A,0),"")&lt;&gt;"","listener-get",IF(IFERROR(MATCH(A9,'listener-post'!$A:$A,0),"")&lt;&gt;"","listener-post",IF(IFERROR(MATCH(A9,'andon-get'!$A:$A,0),"")&lt;&gt;"","andon-get",IF(IFERROR(MATCH(A9,'admin-post'!$A:$A,0),"")&lt;&gt;"","admin-post",IF(IFERROR(MATCH(A9,'admin-put'!$A:$A,0),"")&lt;&gt;"","admin-put",IF(IFERROR(MATCH(A9,'admin-get'!$A:$A,0),"")&lt;&gt;"","admin-get",IF(IFERROR(MATCH(A9,'admin-delete'!$A:$A,0),"")&lt;&gt;"","admin-delete","")))))))</f>
-        <v/>
+        <v>andon-get</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -5308,15 +5397,15 @@
       </c>
       <c r="B10" t="str">
         <f>IFERROR(VLOOKUP($A10,'listener-get'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A10,'listener-post'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A10,'andon-get'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A10,'admin-delete'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A10,'admin-get'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A10,'admin-put'!$A:$D,2,FALSE),IFERROR(VLOOKUP($A10,'admin-post'!$A:$D,2,FALSE),"")))))))</f>
-        <v/>
+        <v>POST</v>
       </c>
       <c r="C10" t="str">
         <f>IFERROR(VLOOKUP($A10,'listener-get'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A10,'listener-post'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A10,'andon-get'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A10,'admin-delete'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A10,'admin-get'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A10,'admin-put'!$A:$D,3,FALSE),IFERROR(VLOOKUP($A10,'admin-post'!$A:$D,3,FALSE),"")))))))</f>
-        <v/>
+        <v>http://localhost:8001/api/users/register</v>
       </c>
       <c r="D10" s="19" t="str">
         <f>IF(IFERROR(MATCH(A10,'listener-get'!$A:$A,0),"")&lt;&gt;"","listener-get",IF(IFERROR(MATCH(A10,'listener-post'!$A:$A,0),"")&lt;&gt;"","listener-post",IF(IFERROR(MATCH(A10,'andon-get'!$A:$A,0),"")&lt;&gt;"","andon-get",IF(IFERROR(MATCH(A10,'admin-post'!$A:$A,0),"")&lt;&gt;"","admin-post",IF(IFERROR(MATCH(A10,'admin-put'!$A:$A,0),"")&lt;&gt;"","admin-put",IF(IFERROR(MATCH(A10,'admin-get'!$A:$A,0),"")&lt;&gt;"","admin-get",IF(IFERROR(MATCH(A10,'admin-delete'!$A:$A,0),"")&lt;&gt;"","admin-delete","")))))))</f>
-        <v/>
+        <v>admin-post</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -5582,51 +5671,51 @@
   <sheetData>
     <row r="1" spans="2:7" s="21" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B1" s="21" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F1" s="21" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="G1" s="21" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="2:7" s="20" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C2" s="20" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="2:7" s="20" customFormat="1" ht="13.5" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="65" t="s">
-        <v>100</v>
-      </c>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
+      <c r="B4" s="102" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="102"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="102"/>
+      <c r="F4" s="102"/>
+      <c r="G4" s="102"/>
     </row>
   </sheetData>
   <mergeCells count="1">
